--- a/Testdata/CandidateValidEmails.xlsx
+++ b/Testdata/CandidateValidEmails.xlsx
@@ -12,24 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
   <si>
     <t>Email</t>
   </si>
   <si>
-    <t>GJBQT@Yopmail.com</t>
-  </si>
-  <si>
-    <t>xOYmk@Yopmail.com</t>
-  </si>
-  <si>
-    <t>BuhXm@Yopmail.com</t>
-  </si>
-  <si>
-    <t>wQwsw@Yopmail.com</t>
-  </si>
-  <si>
-    <t>twWwN@Yopmail.com</t>
+    <t>SRRHS@Yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -74,7 +62,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -89,22 +77,12 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
